--- a/output/2026-09-08_20_Croazia_Sisacko-moslavacka_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-08_20_Croazia_Sisacko-moslavacka_Impiantistica_aspirazione_industriale.xlsx
@@ -494,7 +494,6 @@
           <t>099/5778183</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Contractor/installatore attivo in Sisačko-moslavačka, Zagabria e Karlovac (dal 2019, dir. Hrvoje Rusevljan). Non e' un distributore/rivenditore specializzato in dust collector o filtrazione aria industriale; candidato piu' vicino al settore reperibile nella contea, ma va validato ulteriormente per idoneita' come partner B2B (system integrator ventilazione generalista, non industriale specifico). | Verificato (fonte: fininfo.hr, companywall.hr, tvrtke.hr) - incluso come adiacente/generalista, NON specializzato</t>
@@ -502,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
